--- a/agent_runs/manjidiwang/episodes/ep05/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep05/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>报到与初次寒暄 （，总时长：11秒，镜头数：4个）</t>
+          <t>报到与初次寒暄</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>任务交接与冷笑离场 （，总时长：13秒，镜头数：4个）</t>
+          <t>任务交接与冷笑离场</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>会议室突袭 （，总时长：13秒，镜头数：4个）</t>
+          <t>会议室突袭</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>冲突爆发与攻守对峙 （，总时长：10秒，镜头数：2个）</t>
+          <t>冲突爆发与攻守对峙</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>王海涛倒戈交代 （，总时长：11秒，镜头数：3个）</t>
+          <t>王海涛倒戈交代</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>证据摊牌 （，总时长：13秒，镜头数：4个）</t>
+          <t>证据摊牌</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>抽刀逼问 （，总时长：14秒，镜头数：3个）</t>
+          <t>抽刀逼问</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>冷静解剖刀刺后果 （，总时长：11秒，镜头数：4个）</t>
+          <t>冷静解剖刀刺后果</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>心理击溃 （，总时长：10秒，镜头数：2个）</t>
+          <t>心理击溃</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>递刀与交易 （，总时长：12秒，镜头数：3个）</t>
+          <t>递刀与交易</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>关门与心理余震 （，总时长：12秒，镜头数：3个）</t>
+          <t>关门与心理余震</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
